--- a/automation/badi_besuch_ase/meta_ssd_badibesuch.xlsx
+++ b/automation/badi_besuch_ase/meta_ssd_badibesuch.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssdbry0a\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1056EA-2919-4B5E-960B-67BED30E72DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BFB09A-7472-4982-BFCF-892B448BC3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1053,11 +1053,11 @@
     <t>vor 5 Tagen  – heute</t>
   </si>
   <si>
-    <t>Die dargestellten Zahlen stammen direkt von den Sensoren, die in der Nähe der Kassen aufgestellt sind. Die Sensordaten entsprechen nicht genau den bezahlten Eintritten. Erfahrungsgemäss sind die Sensordaten etwa 20 % höher als die bezahlten Eintritte. Das liegt daran, dass die Sensoren auch weiterzählen, wenn z. B. Kinder im Kassenbereich hin und her laufen.
+    <t>Die dargestellten Zahlen stammen direkt von den Sensoren, die in der Nähe der Kassen aufgestellt sind. Die Sensordaten entsprechen nicht genau den Eintritten. Erfahrungsgemäss sind die Sensordaten etwa 20 % höher als die Eintritte. Das liegt daran, dass die Sensoren mehrfach zählen, wenn Personen das Bad verlassen und wieder betreten oder wenn z. B. Kinder im Kassenbereich hin und herlaufen.
 Die Sensoren bleiben im Winterbetrieb aktiv.</t>
   </si>
   <si>
-    <t>Enthalten sind jene Hallen- und Sommerbäder, die vom Sportamt betrieben werden. Einige Fremdbetriebene Bäder (Dolder, Schanzengraben), Gratisbäder und Bäder im Umbau werden nicht aufgeführt.</t>
+    <t>Enthalten sind jene Hallen- und Freibäder, die vom Sportamt betrieben werden. In einigen fremdbetriebene Bädern (Dolder, Schanzengraben), Gratisbäder und Bäder im Umbau werden keine Daten erfasst und sie sind darum nicht aufgeführt.</t>
   </si>
 </sst>
 </file>
@@ -1782,19 +1782,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="255.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="255.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="14.08203125" style="11" customWidth="1"/>
     <col min="2" max="2" width="24.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="66.875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="53.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="66.83203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="53.58203125" style="5" customWidth="1"/>
     <col min="5" max="5" width="8.75" style="5" customWidth="1"/>
-    <col min="6" max="6" width="88.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="50.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="88.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="50.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="255.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="4" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" s="4" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>7</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="4" customFormat="1" ht="127.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" s="4" customFormat="1" ht="143" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>11</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>14</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>17</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>21</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>24</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>27</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>30</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>33</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>36</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>39</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>42</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>46</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>50</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>53</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A17" s="33" t="s">
         <v>56</v>
       </c>
@@ -2099,14 +2099,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
       <c r="B18" s="3"/>
       <c r="C18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>60</v>
       </c>
@@ -2119,7 +2119,7 @@
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B20" s="13" t="s">
         <v>8</v>
       </c>
@@ -2129,7 +2129,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>62</v>
       </c>
@@ -2142,7 +2142,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:6" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>62</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="43.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="43" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>62</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="75" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>62</v>
       </c>
@@ -2187,13 +2187,13 @@
       <c r="D24" s="1"/>
       <c r="E24" s="7"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
       <c r="D25" s="1"/>
       <c r="E25" s="7"/>
     </row>
-    <row r="26" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -2201,7 +2201,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>65</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
       <c r="B28" s="13" t="s">
         <v>68</v>
@@ -2235,7 +2235,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>72</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>72</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>72</v>
       </c>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="E31" s="7"/>
     </row>
-    <row r="32" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>72</v>
       </c>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="E32" s="7"/>
     </row>
-    <row r="33" spans="1:5" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" s="4" customFormat="1" ht="25" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>72</v>
       </c>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="E33" s="7"/>
     </row>
-    <row r="34" spans="1:5" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" s="4" customFormat="1" ht="25" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>72</v>
       </c>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="E34" s="7"/>
     </row>
-    <row r="35" spans="1:5" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" s="4" customFormat="1" ht="25" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>72</v>
       </c>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="E35" s="7"/>
     </row>
-    <row r="36" spans="1:5" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" s="4" customFormat="1" ht="25" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>72</v>
       </c>
@@ -2361,21 +2361,21 @@
       </c>
       <c r="E36" s="7"/>
     </row>
-    <row r="37" spans="1:5" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A37" s="11"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
     </row>
-    <row r="38" spans="1:5" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
     </row>
-    <row r="39" spans="1:5" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A39" s="11"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2391,131 +2391,131 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.375" style="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" style="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.625" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.875" style="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.375" style="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.125" style="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.375" style="24" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.875" style="24" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.625" style="24" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.375" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.58203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.58203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.83203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.58203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" style="24" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.75" style="24" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.625" style="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.875" style="24" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.58203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" style="24" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="11" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A5" s="29" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A6" s="29" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A7" s="29" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A8" s="29" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A9" s="29" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A10" s="29" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A11" s="29" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A12" s="29" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A13" s="29" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A14" s="29" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A15" s="29" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A16" s="29" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A17" s="29" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A18" s="29" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A19" s="29" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A20" s="29" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="31" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="32" t="s">
         <v>96</v>
       </c>
@@ -2532,14 +2532,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5" style="24" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="24" customWidth="1"/>
+    <col min="2" max="2" width="5.58203125" style="24" customWidth="1"/>
     <col min="3" max="16384" width="11" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>75</v>
       </c>
@@ -2547,27 +2547,27 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A5" s="29" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A6" s="30" t="s">
         <v>101</v>
       </c>
@@ -2575,12 +2575,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="31" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="32" t="s">
         <v>96</v>
       </c>
@@ -2597,14 +2597,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.375" style="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.33203125" style="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.25" style="24" customWidth="1"/>
     <col min="3" max="16384" width="11" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>75</v>
       </c>
@@ -2612,118 +2612,118 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A5" s="29" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A6" s="29" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A7" s="29" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A8" s="29" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A9" s="29" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A10" s="29" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A11" s="29" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A12" s="29" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A13" s="29" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A14" s="29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A15" s="29" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A16" s="29" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A18" s="26"/>
     </row>
-    <row r="19" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A19" s="26"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="31" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="32" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A22" s="26"/>
     </row>
-    <row r="23" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A23" s="26"/>
     </row>
-    <row r="24" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A24" s="26"/>
     </row>
-    <row r="25" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A25" s="26"/>
     </row>
-    <row r="26" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A26" s="26"/>
     </row>
-    <row r="27" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A27" s="26"/>
     </row>
   </sheetData>
@@ -2738,15 +2738,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.5" style="24" customWidth="1"/>
-    <col min="2" max="2" width="5.375" style="24" customWidth="1"/>
-    <col min="3" max="3" width="58.625" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" style="24" customWidth="1"/>
+    <col min="3" max="3" width="58.58203125" style="24" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="11" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>75</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
         <v>119</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
         <v>122</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
         <v>125</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A5" s="29" t="s">
         <v>128</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
         <v>58</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
         <v>133</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
         <v>136</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A9" s="29" t="s">
         <v>139</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A10" s="29" t="s">
         <v>142</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A11" s="29" t="s">
         <v>144</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A12" s="29" t="s">
         <v>146</v>
       </c>
@@ -2889,7 +2889,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A13" s="29" t="s">
         <v>148</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A14" s="29" t="s">
         <v>151</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A15" s="29" t="s">
         <v>154</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A16" s="29" t="s">
         <v>156</v>
       </c>
@@ -2937,12 +2937,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="31" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A22" s="32" t="s">
         <v>96</v>
       </c>
@@ -2958,15 +2958,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="637d3f4c-beee-42dd-a17b-93f7589025e5" xsi:nil="true"/>
@@ -2977,7 +2968,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010036EB69643BC4D84A90CF31D6917ED8B0" ma:contentTypeVersion="17" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e787fa9c9cb978e1d00e8cc5d4e605d2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31d8624d-d3e1-4449-addd-518bfa42d279" xmlns:ns3="637d3f4c-beee-42dd-a17b-93f7589025e5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="369004915ca410f163a62304f925ff92" ns2:_="" ns3:_="">
     <xsd:import namespace="31d8624d-d3e1-4449-addd-518bfa42d279"/>
@@ -3226,15 +3217,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B3AD83-9986-4E71-995F-A94C1CED6EB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6056489-A7A4-4445-AFC5-87E5586E5E93}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3251,7 +3243,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B249E2D-022F-440D-B037-6C32F5252DA3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3268,4 +3260,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B3AD83-9986-4E71-995F-A94C1CED6EB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/automation/badi_besuch_ase/meta_ssd_badibesuch.xlsx
+++ b/automation/badi_besuch_ase/meta_ssd_badibesuch.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssdbry0a\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sszgua\git\opendatazurich.github.io\automation\badi_besuch_ase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BFB09A-7472-4982-BFCF-892B448BC3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D29C9B-AEDB-4C08-9607-D01657D541D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="14" r:id="rId1"/>
@@ -942,9 +942,6 @@
     <t>Freizeit</t>
   </si>
   <si>
-    <t>baden, schwimmen, badi, freibad, hallenbad, sport</t>
-  </si>
-  <si>
     <t>Bäder:</t>
   </si>
   <si>
@@ -1023,9 +1020,6 @@
     <t>Sportamt, Schul- und Sportdepartement</t>
   </si>
   <si>
-    <t>Badi Besuchende</t>
-  </si>
-  <si>
     <t>Datenerhebung:</t>
   </si>
   <si>
@@ -1035,29 +1029,34 @@
     <t>Datenquelle:</t>
   </si>
   <si>
-    <t>[ASE Diamond API](https://zuerich.pas.ch/)</t>
-  </si>
-  <si>
-    <t>Detaillierte Informationen finden Sie auf der Webseite [Badi aktuell](https://www.stadt-zuerich.ch/de/stadtleben/sport-und-erholung/sport-und-badeanlagen/sommerbaeder/badi-aktuell.html).</t>
-  </si>
-  <si>
     <t>Name des Standortes</t>
   </si>
   <si>
-    <t>Dieser Datensatz enthält Besuchsfrequenzen in Badeanlagen der Stadt Zürich. 
-Es gibt zwei separate Dateien, die über das Attribut `LocationId` verknüpft werden können. 
-- **Badi_Besuch.csv**: Enthält die tatsächlichen Besuchsfrequenzen. Die Zahlen werden durch Sensoren automatisch erhoben und sind in 5-Minuten-Abschnitten zusammengefasst.
-- **Badi_Koordinaten.csv**: Enthält die Koordinaten der einzelnen Standorte.</t>
-  </si>
-  <si>
     <t>vor 5 Tagen  – heute</t>
   </si>
   <si>
-    <t>Die dargestellten Zahlen stammen direkt von den Sensoren, die in der Nähe der Kassen aufgestellt sind. Die Sensordaten entsprechen nicht genau den Eintritten. Erfahrungsgemäss sind die Sensordaten etwa 20 % höher als die Eintritte. Das liegt daran, dass die Sensoren mehrfach zählen, wenn Personen das Bad verlassen und wieder betreten oder wenn z. B. Kinder im Kassenbereich hin und herlaufen.
-Die Sensoren bleiben im Winterbetrieb aktiv.</t>
-  </si>
-  <si>
-    <t>Enthalten sind jene Hallen- und Freibäder, die vom Sportamt betrieben werden. In einigen fremdbetriebene Bädern (Dolder, Schanzengraben), Gratisbäder und Bäder im Umbau werden keine Daten erfasst und sie sind darum nicht aufgeführt.</t>
+    <t>Datenreihe «Anzahl der Badegäste»</t>
+  </si>
+  <si>
+    <t>Dieser Datensatz enthält eine Datenreihe mit der «Anzahl der Badegäste» (Besuchsfrequenzen) in den Badeanlagen der Stadt Zürich. Es handelt sich um Sensordaten, die rund 20 Prozent höher sind als die effektiven Eintrittszahlen/Kassenzahlen (Eintritte). Siehe auch unten unter «Datenerhebung».
+Es gibt zwei separate Dateien, die über das Attribut `LocationId` verknüpft werden können.
+- **Badi_Besuch.csv**: Enthält die Anzahl der Badegäste. Die Zahlen werden durch Sensoren automatisch erhoben und sind in 5-Minuten-Abschnitten zusammengefasst.
+- **Badi_Koordinaten.csv**: Enthält die Koordinaten der einzelnen Badi-Standorte.</t>
+  </si>
+  <si>
+    <t>baden, schwimmen, badi, freibad, hallenbad, sport, sommerbad</t>
+  </si>
+  <si>
+    <t>[ASE Diamond API](https://arlas.ase.solutions/v2/swagger/index.html)</t>
+  </si>
+  <si>
+    <t>Im Datensatz enthalten sind die Hallen- und Sommerbäder der Stadt Zürich mit folgenden Ausnahmen: Flussbad Au-Höngg und Seebad Katzensee (weil keine Sensordaten erfasst werden), gewisse Bäder, die von Dritten betrieben werden (Seebad Enge und Hallenbad Altstetten), Bäder im Umbau.</t>
+  </si>
+  <si>
+    <t>Weitere Informationen finden Sie auf der Webseite  [Badi aktuell](https://www.stadt-zuerich.ch/badi-aktuell).</t>
+  </si>
+  <si>
+    <t>Die dargestellten Zahlen (Datenreihe «Anzahl der Badegäste») stammen direkt von den Sensoren, die in der Nähe der Kassen aufgestellt sind. Diese Sensordaten entsprechen nicht genau der Anzahl Badegästen. Erfahrungsgemäss sind die Sensordaten etwa 20 Prozent höher als die Eintrittszahlen/Kassenzahlen (Eintritte). Das liegt daran, dass die Sensoren mehrfach zählen, wenn Personen das Bad verlassen und wieder betreten oder wenn zum Beispiel Kinder im Kassenbereich hin und herlaufen. Die Sensoren bleiben im Winterbetrieb aktiv.</t>
   </si>
 </sst>
 </file>
@@ -1782,19 +1781,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="255.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="255.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.08203125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="14.125" style="11" customWidth="1"/>
     <col min="2" max="2" width="24.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="66.83203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="53.58203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="66.875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="53.625" style="5" customWidth="1"/>
     <col min="5" max="5" width="8.75" style="5" customWidth="1"/>
-    <col min="6" max="6" width="88.83203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="50.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="88.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="50.375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="255.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1817,7 +1816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="4" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" s="4" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
         <v>7</v>
       </c>
@@ -1828,14 +1827,14 @@
         <v>9</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="4" customFormat="1" ht="143" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" s="4" customFormat="1" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>11</v>
       </c>
@@ -1846,14 +1845,14 @@
         <v>9</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>14</v>
       </c>
@@ -1871,7 +1870,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>17</v>
       </c>
@@ -1887,7 +1886,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>21</v>
       </c>
@@ -1905,7 +1904,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>24</v>
       </c>
@@ -1916,14 +1915,14 @@
         <v>9</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>27</v>
       </c>
@@ -1934,14 +1933,14 @@
         <v>9</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>30</v>
       </c>
@@ -1952,14 +1951,14 @@
         <v>9</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>33</v>
       </c>
@@ -1975,7 +1974,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>36</v>
       </c>
@@ -1986,14 +1985,14 @@
         <v>19</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>39</v>
       </c>
@@ -2009,7 +2008,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
         <v>42</v>
       </c>
@@ -2027,7 +2026,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>46</v>
       </c>
@@ -2045,7 +2044,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>50</v>
       </c>
@@ -2056,14 +2055,14 @@
         <v>9</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>53</v>
       </c>
@@ -2081,7 +2080,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="33" t="s">
         <v>56</v>
       </c>
@@ -2099,14 +2098,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="11"/>
       <c r="B18" s="3"/>
       <c r="C18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
         <v>60</v>
       </c>
@@ -2119,7 +2118,7 @@
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B20" s="13" t="s">
         <v>8</v>
       </c>
@@ -2129,28 +2128,28 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>62</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:6" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="7"/>
@@ -2158,15 +2157,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="43" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="43.5" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
         <v>62</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="7"/>
@@ -2174,26 +2173,26 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="75" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
         <v>62</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="7"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
       <c r="D25" s="1"/>
       <c r="E25" s="7"/>
     </row>
-    <row r="26" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="11"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -2201,7 +2200,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
         <v>65</v>
       </c>
@@ -2219,7 +2218,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="11"/>
       <c r="B28" s="13" t="s">
         <v>68</v>
@@ -2235,147 +2234,147 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
         <v>72</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C29" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D29" s="21" t="s">
         <v>171</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>172</v>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
         <v>72</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
         <v>72</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E31" s="7"/>
     </row>
-    <row r="32" spans="1:6" s="4" customFormat="1" ht="12.5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
         <v>72</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E32" s="7"/>
     </row>
-    <row r="33" spans="1:5" s="4" customFormat="1" ht="25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
         <v>72</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C33" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D33" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="D33" s="21" t="s">
-        <v>175</v>
-      </c>
       <c r="E33" s="7"/>
     </row>
-    <row r="34" spans="1:5" s="4" customFormat="1" ht="25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
         <v>72</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E34" s="7"/>
     </row>
-    <row r="35" spans="1:5" s="4" customFormat="1" ht="25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
         <v>72</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E35" s="7"/>
     </row>
-    <row r="36" spans="1:5" s="4" customFormat="1" ht="25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
         <v>72</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C36" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="D36" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="D36" s="21" t="s">
-        <v>185</v>
-      </c>
       <c r="E36" s="7"/>
     </row>
-    <row r="37" spans="1:5" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="11"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
     </row>
-    <row r="38" spans="1:5" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="11"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
     </row>
-    <row r="39" spans="1:5" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="11"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2391,131 +2390,131 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.375" style="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.58203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.58203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.08203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.83203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.58203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.625" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" style="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="24" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.375" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.375" style="24" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.875" style="24" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.625" style="24" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.375" style="24" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.75" style="24" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.58203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.83203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.625" style="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.875" style="24" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="11" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="29" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="29" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="29" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="29" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="29" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="29" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="29" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="29" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="29" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="29" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="29" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="29" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="29" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="29" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="31" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="32" t="s">
         <v>96</v>
       </c>
@@ -2532,14 +2531,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" style="24" customWidth="1"/>
-    <col min="2" max="2" width="5.58203125" style="24" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="24" customWidth="1"/>
     <col min="3" max="16384" width="11" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>75</v>
       </c>
@@ -2547,27 +2546,27 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="29" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="29" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A6" s="30" t="s">
         <v>101</v>
       </c>
@@ -2575,12 +2574,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="31" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="32" t="s">
         <v>96</v>
       </c>
@@ -2597,14 +2596,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.375" style="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.25" style="24" customWidth="1"/>
     <col min="3" max="16384" width="11" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>75</v>
       </c>
@@ -2612,118 +2611,118 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="29" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="29" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="29" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="29" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="29" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="29" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="29" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="29" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="29" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="29" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A17" s="30" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="26"/>
     </row>
-    <row r="19" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="26"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="31" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="32" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="26"/>
     </row>
-    <row r="23" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="26"/>
     </row>
-    <row r="24" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="26"/>
     </row>
-    <row r="25" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="26"/>
     </row>
-    <row r="26" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="26"/>
     </row>
-    <row r="27" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="26"/>
     </row>
   </sheetData>
@@ -2738,15 +2737,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" style="24" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" style="24" customWidth="1"/>
-    <col min="3" max="3" width="58.58203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.375" style="24" customWidth="1"/>
+    <col min="3" max="3" width="58.625" style="24" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="11" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>75</v>
       </c>
@@ -2757,7 +2756,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="29" t="s">
         <v>119</v>
       </c>
@@ -2769,7 +2768,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="29" t="s">
         <v>122</v>
       </c>
@@ -2781,7 +2780,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
         <v>125</v>
       </c>
@@ -2793,7 +2792,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
         <v>128</v>
       </c>
@@ -2805,7 +2804,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="27" t="s">
         <v>58</v>
       </c>
@@ -2817,7 +2816,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="27" t="s">
         <v>133</v>
       </c>
@@ -2829,7 +2828,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="27" t="s">
         <v>136</v>
       </c>
@@ -2841,7 +2840,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="29" t="s">
         <v>139</v>
       </c>
@@ -2853,7 +2852,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="29" t="s">
         <v>142</v>
       </c>
@@ -2865,7 +2864,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
         <v>144</v>
       </c>
@@ -2877,7 +2876,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
         <v>146</v>
       </c>
@@ -2889,7 +2888,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="29" t="s">
         <v>148</v>
       </c>
@@ -2901,7 +2900,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="29" t="s">
         <v>151</v>
       </c>
@@ -2913,7 +2912,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="29" t="s">
         <v>154</v>
       </c>
@@ -2925,7 +2924,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="29" t="s">
         <v>156</v>
       </c>
@@ -2937,12 +2936,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="31" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="32" t="s">
         <v>96</v>
       </c>
@@ -2958,14 +2957,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="637d3f4c-beee-42dd-a17b-93f7589025e5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="31d8624d-d3e1-4449-addd-518bfa42d279">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3218,27 +3215,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="637d3f4c-beee-42dd-a17b-93f7589025e5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="31d8624d-d3e1-4449-addd-518bfa42d279">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6056489-A7A4-4445-AFC5-87E5586E5E93}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B3AD83-9986-4E71-995F-A94C1CED6EB8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="637d3f4c-beee-42dd-a17b-93f7589025e5"/>
-    <ds:schemaRef ds:uri="31d8624d-d3e1-4449-addd-518bfa42d279"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3263,9 +3253,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B3AD83-9986-4E71-995F-A94C1CED6EB8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6056489-A7A4-4445-AFC5-87E5586E5E93}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="637d3f4c-beee-42dd-a17b-93f7589025e5"/>
+    <ds:schemaRef ds:uri="31d8624d-d3e1-4449-addd-518bfa42d279"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>